--- a/reference/kahoot/out/kahoot-10/kahoot-10.xlsx
+++ b/reference/kahoot/out/kahoot-10/kahoot-10.xlsx
@@ -467,27 +467,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Блок схем дээр "давталт" гэдгийг юу харуулдаг вэ?</t>
+          <t>1000₮-ийн 3 талх сагсалсан. Кассын дэлгэцэнд юу гарах вэ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Хоёр ромбо дараалж зурах</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ромбо руу буцаж ирэх сум</t>
+          <t>100010001000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Тэгш өнцөгтийг олон удаа зурах</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Төгсгөл (зууван) байхгүй байх</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -539,27 +539,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000₮, 2000₮, 3000₮ хийсэн. Хадгаламжид хэд байх вэ?</t>
+          <t>Ухаалаг цаг: 3 өдөр, өдөр бүр 5000 алхсан. Нийт хэд гэж гарах вэ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3000₮</t>
+          <t>5000 алхам</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6000₮</t>
+          <t>15000 алхам</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0₮</t>
+          <t>0 алхам</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1000₮</t>
+          <t>10000 алхам</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -611,22 +611,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Кинонд 3 од (*) өгөв. Хэдэн цонх гарах вэ?</t>
+          <t>Утас 3 зураас болтол цэнэглэгдлээ. Хэдэн цонх гарах вэ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1 цонх: ***</t>
+          <t>1 цонх: ███</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3 цонх: *, **, ***</t>
+          <t>3 цонх: █, ██, ███</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3 цонх, бүгд *</t>
+          <t>3 цонх, бүгд █</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Хуудсаа нээхэд юу болох вэ?</t>
+          <t>Хоолоо 30 секунд халаалаа. Хуудсаа нээхэд юу болох вэ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 9 8 … 1 Шинэ жил мэнд!</t>
+          <t>30 29 28 … 1 Дзинь!</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Шинэ жил мэнд!</t>
+          <t>Дзинь!</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10 Шинэ жил мэнд!</t>
+          <t>30 Дзинь!</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -683,27 +683,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4 найз хэдэн янзаар эгнэж зогсох вэ? (1 × 2 × 3 × 4)</t>
+          <t>Бактери цаг бүр 2 дахин олширно. 5 цагийн дараа код хэдийг харуулах вэ?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0 янзаар</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24 янзаар</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10 янзаар</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 янзаар</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -719,34 +719,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Кактусаа 3 хоног тутамд услана. 10 хоногт хэдэн удаа услах вэ?</t>
+          <t>Автобус 15 минут тутамд ирнэ. 1 цагт хэдэн автобус ирэх вэ?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4 удаа</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10 удаа</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30 удаа</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3 удаа</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>60</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -755,7 +755,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Пуужин хөөргөхөд 5 4 3 2 1 гэж тоолох аль мөр вэ?</t>
+          <t>Лифт зөвхөн тэгш давхарт (2–10) зогсоно. Аль мөр зөв вэ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
         <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -791,7 +791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Үнийн хүснэгт нэг мөрөнд наалдчихлаа. Юу дутуу вэ?</t>
+          <t>Хуваарь нэг мөрөнд наалдчихлаа. Юу дутуу вэ?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -827,34 +827,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Энэ давталт хэдэн удаа ажиллах вэ?</t>
+          <t>Ангид 25 сурагч бий. Багш хэдэн удаа нэр дуудах вэ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -863,34 +863,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 нүдэнд 1, 2, 4 будаа (нийт 7) тавих ёстой. Код юу гаргах вэ?</t>
+          <t>10, 15, 20 удаа суниана (нийт 45). Код юу гаргах вэ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7 будаа</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15 будаа</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8 будаа</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14 будаа</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>60</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
